--- a/output/gaines_taxonomy_match.xlsx
+++ b/output/gaines_taxonomy_match.xlsx
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Acne treatment</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78.3</v>
+        <v>92</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62.5</v>
+        <v>89.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Textile treatment baths</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>59.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -502,27 +502,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evaporation inhibitors for gasoline</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.1</v>
+        <v>86.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wash and care agents for vinyl and cork linoleum</t>
+          <t>Fluxing agents in solder paste</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lubricant for electric circuit breakers</t>
+          <t>Epoxy-based semiconductor case</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>47.1</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -549,11 +549,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welding and soldering agent in general</t>
+          <t>Polymer processing aids (PPAs) in the production of rubber and non-plastic packaging uses, especially in cases where thermoplastics are used</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>44.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lubricant for music instruments</t>
+          <t>PVC membrane for roofing</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -603,19 +603,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PVC membrane for roofing</t>
+          <t>Antistats in rubber and plastic compositions</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Antistats in rubber and plastic compositions</t>
+          <t>Sealants for flange faces (chemicals)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="7">
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brow products</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>76.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beef and beef products</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fish and fish products</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>70.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -688,27 +688,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="10">
@@ -719,27 +719,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="11">
@@ -750,27 +750,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agent suppressing acid mist</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>87.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Flame retardant for polycarbonate resins</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>80.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>78.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -781,27 +781,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zinc batteries</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>78.3</v>
+        <v>93.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Etching of aluminum</t>
+          <t>Leather outdoor wear</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Solution for etching and polishing of glass</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>71.59999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -812,27 +812,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Zinc battery surfactant</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Zinc batteries</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Pipes and pipe components</t>
-        </is>
-      </c>
       <c r="G13" t="n">
-        <v>71.8</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -843,27 +843,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bathroom ceramics</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shower panels</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>63.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etch cleaning fluid</t>
+          <t>Metal cleaners</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>59.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -874,28 +874,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fluorinated industrial metal cleaning and degreasing solvent</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39.7</v>
+        <v>83.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Flame retardants and extinguishing agents</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>38.9</v>
+        <v>81.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Processing aid (surfactant, bath stabilization) (information received in the
-consultation on the Annex XV report in 2023)</t>
+          <t>Portable or fixed fire extinguisher</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="16">
@@ -906,28 +905,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42.4</v>
+        <v>83.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Processing aid (surfactant, bath stabilization) (information received in the
-consultation on the Annex XV report in 2023)</t>
+          <t>Flame retardants and extinguishing agents</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.7</v>
+        <v>81.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inert reaction media in chemical reactions (especially with gaseous reactants)</t>
+          <t>Portable or fixed fire extinguisher</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>38.9</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="17">
@@ -938,27 +936,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71.8</v>
+        <v>87</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="18">
@@ -969,27 +967,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>58.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="19">
@@ -1000,27 +998,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>58.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="20">
@@ -1031,27 +1029,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>X-ray film for medical and industrial use</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>69.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lubricant for industrial printers</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>59.6</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1062,27 +1060,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>58.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="22">
@@ -1097,15 +1095,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PVC membrane for roofing</t>
+          <t>Iron-Flow batteries</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>66.7</v>
+        <v>79.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1113,7 +1111,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>65.09999999999999</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="23">
@@ -1128,23 +1126,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Breathing air devices</t>
+          <t>Iron-Flow batteries</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>68.8</v>
+        <v>79.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PVC membrane for roofing</t>
+          <t>EV refrigerant circuit / EV battery system</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="24">
@@ -1155,27 +1153,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>PTFE membrane for filter bags used in baghouses</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>PVC membrane for roofing</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>45.2</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>"A patent describes the use of fluorocarbon surfactants in asulfuric acid‐chromic acid bath for a pre‐etch stage to conditionplastic parts before plating. The patent states that the bath shouldcontain about 4–12 ounces of fluorocarbon surfactant per 100gallons of bath. 132 Another patent describes etching steel beforeplating. The etching is performed in a bath with a strong mineral acidand perfluorocarbon sulfonic acids. 133 PFSAs have been used as analuminum etchant134 in solutions for glass etching, for planar etchingof fused silica, and as wetting agents in plastic etching.11 Anotherpatent describes the use of etching glass to reduce display surfaces'specular reflection in many hand‐held and touch‐sensitive electronicdevices. A fluorine‐based smudge‐resistant layer is added to the glassby a reaction with the glass and a fluorosilane, which contains PFASmoieties" (p. 360)</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>42.9</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Waxes used as additives for printing inks</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>42.4</v>
       </c>
     </row>
     <row r="25">
@@ -1190,7 +1188,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1198,7 +1196,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>64.3</v>
+        <v>79.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1206,7 +1204,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
@@ -1217,27 +1215,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Solvent in chemical reactions</t>
+          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>55</v>
+        <v>50.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>CT contrast agent</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>52.4</v>
+        <v>45.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
+          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>51.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="27">
@@ -1248,27 +1246,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>49.3</v>
+        <v>92</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>An U.S.military specification for a delay composition of tungsten andfluorocarbon copolymer calls for the copolymer to be one percentof the composition (p. 360)</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>47</v>
+        <v>89.3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>44.5</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="28">
@@ -1279,27 +1277,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peptide manufacturing</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>76.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fluid for electronics testing</t>
+          <t>Cleaning of metal surfaces</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>68.2</v>
+        <v>83</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anti-drip agent for electronics</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>65.2</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1310,27 +1308,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Etching of aluminum</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>59.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="30">
@@ -1341,27 +1339,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agent suppressing acid mist</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>74.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Solution for etching and polishing of glass</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>71.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>62.5</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="31">
@@ -1372,27 +1370,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coating for PE film</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>73.3</v>
+        <v>92</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Skin powder</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>70.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ball valve</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>66.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="32">
@@ -1403,27 +1401,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coating for PE film</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>73.3</v>
+        <v>92</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PTFE tape for household applications</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>61.5</v>
+        <v>89.3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piping and tubing for drinking water applications</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>58</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="33">
@@ -1434,27 +1432,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coating for PE film</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.3</v>
+        <v>92</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PTFE tape for household applications</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>61.5</v>
+        <v>89.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piping and tubing for drinking water applications</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>58</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="34">
@@ -1465,27 +1463,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Battery electrode binder</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Zinc batteries</t>
+          <t>Multilayer circuit board</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>78.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Insulated electrical wires</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>76.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="35">
@@ -1496,27 +1494,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Bedding</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>92</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Binders for plastic bonded explosives (PBX)</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>89.7</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Plastic bonded explosives (PBX)</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>85.2</v>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Antistats in rubber and plastic compositions</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>76.09999999999999</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="36">
@@ -1527,27 +1525,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Bedding</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>92</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Multilayer circuit board</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Binders for plastic bonded explosives (PBX)</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="G36" t="n">
         <v>89.7</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Plastic bonded explosives (PBX)</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Coating for PE film</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>73.3</v>
       </c>
     </row>
     <row r="37">
@@ -1589,27 +1587,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coating for PE film</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>73.3</v>
+        <v>92</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cyrogenic storage tanks</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>72.2</v>
+        <v>89.3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>O&amp;G tanks</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>71.40000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="39">
@@ -1624,7 +1622,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>60.9</v>
+        <v>90.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1632,15 +1630,15 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>51.4</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cured epoxy resin remover</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>43.8</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="40">
@@ -1655,23 +1653,23 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>60.9</v>
+        <v>90.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Artificial replacement heart valve</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>48.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>42.5</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1682,27 +1680,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nail polish</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>70.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Skin creams</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>70.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Environmental contol systems (ECS)</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>55.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1725,11 +1723,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>47.9</v>
+        <v>48.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agent wetting sulfuric acid or cyanide to leach ore</t>
+          <t>"Machine parts have been cleanedafter nickel plating with a solution containing PFOS."</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -1744,27 +1742,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Beaded retroreflective road sheeting</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>44.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fiber optic cables</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>44.1</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Insulated heating cables</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>43.1</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1775,27 +1773,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Table cloths</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>66.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Etching solution for plastic etching followed by electroplating (e.g. chrome)</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>40.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inert reaction media in chemical reactions (especially with gaseous reactants)</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>40</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1806,27 +1804,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>71.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>71.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1837,27 +1835,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>78.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zinc batteries</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>78.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1868,27 +1866,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>78.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>62.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1899,27 +1897,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>78.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>62.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>58.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1930,27 +1928,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liquid chromatography columns</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>65.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Reverse phase liquid chromatography solvents</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>64.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liquid chromatography instruments</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>59.6</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1961,27 +1959,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Peptide manufacturing</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>76.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fluoropolymer films for roofing</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>59.1</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fluoropolymer fabrics for roofing</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>56.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1992,27 +1990,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>78.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>62.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>58.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2023,27 +2021,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>78.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Zinc batteries</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>78.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Battery electrolyte solution / electrolyte additive</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>67.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2062,19 +2060,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Protective anti-static clothing (e.g. tank trucks)</t>
+          <t>Decorative chrome plating solution (metal plating)</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>49</v>
+        <v>46.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Decorative chrome plating solution (metal plating)</t>
+          <t>Recreational yachts (large)</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>46.9</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="54">
@@ -2089,23 +2087,23 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>66.7</v>
+        <v>93.2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table cloths</t>
+          <t>Leather outdoor wear</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>66.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dye transfer material</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>55.2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55">
@@ -2116,27 +2114,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Protective anti-static clothing (e.g. tank trucks)</t>
+          <t>Metal cleaners</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>49</v>
+        <v>46.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Anti-fog agents / spray</t>
+          <t>Alkaline cleaner</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Textile treatment sprays and creams (leather and others)</t>
+          <t>Ceramic cleaners</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
@@ -2155,19 +2153,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Textile treatment sprays and creams (leather and others)</t>
+          <t>Perfumes and fragrances</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>52.3</v>
+        <v>48.8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Protective anti-static clothing (e.g. tank trucks)</t>
+          <t>Dishes and glass cleaners</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>49.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="57">
@@ -2209,27 +2207,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C58" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Heat resistant packaging</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Folding packaging cartons</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>81.8</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Blood bags</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Dye transfer material</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>55.2</v>
       </c>
     </row>
     <row r="59">
@@ -2240,27 +2238,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Heat resistant packaging</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Folding packaging cartons</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>81.8</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Blood bags</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Dye transfer material</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>55.2</v>
       </c>
     </row>
     <row r="60">
@@ -2279,19 +2277,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Reverse phase liquid chromatography solvents</t>
+          <t>Liquid chromatography instruments</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>64.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liquid chromatography instruments</t>
+          <t>Photoresist liquid</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>59.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
@@ -2395,27 +2393,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General protective gloves</t>
+          <t>Respiratory protective equipment</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>57.1</v>
+        <v>47.6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Respiratory protective equipment</t>
+          <t>Coatings over reactive metallic powders (e.g. aluminum)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coatings over reactive metallic powders (e.g. aluminum)</t>
+          <t>Disposable medical protective footwear</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="65">
@@ -2426,27 +2424,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>71.8</v>
+        <v>93.2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Leather outdoor wear</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>71.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ionic liquids</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66">
@@ -2457,27 +2455,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dye transfer material</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>55.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lubricant for metal food and beverage containers</t>
+          <t>Heat resistant packaging</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>52.4</v>
+        <v>82.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>General food case materials</t>
+          <t>Folding packaging cartons</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>51.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="67">
@@ -2519,27 +2517,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Heat resistant packaging</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Folding packaging cartons</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
         <v>81.8</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Paper food straws</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Kraft paper</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>62.5</v>
       </c>
     </row>
     <row r="69">
@@ -2566,7 +2564,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Extruded polystyrene foam (XPS) boards</t>
+          <t>Leather bags</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2581,27 +2579,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C70" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Heat resistant packaging</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Folding packaging cartons</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
         <v>81.8</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Blood bags</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Dye transfer material</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>55.2</v>
       </c>
     </row>
     <row r="71">
@@ -2612,27 +2610,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>Streaming fire-extinguishing agent</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Flame retardants and extinguishing agents</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Streaming fire-extinguishing agent</t>
-        </is>
-      </c>
       <c r="G71" t="n">
-        <v>57.5</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2674,27 +2672,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>PTFE wax</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>Fluoropolymer processing aid for PTFE</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Fluoropolymer processing aid for PVDF</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>PTFE wax</t>
-        </is>
-      </c>
       <c r="G73" t="n">
-        <v>66.7</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -2705,11 +2703,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fluoropolymer processing aid for FEP</t>
+          <t>Fluoropolymer processing aid for PVDF</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>87.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2736,27 +2734,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Environmental contol systems (ECS)</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>55.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Solvent in chemical reactions</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>55</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>52.4</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -2767,27 +2765,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Environmental contol systems (ECS)</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>55.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Solvent in chemical reactions</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>55</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>52.4</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -2798,27 +2796,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Environmental contol systems (ECS)</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>55.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Solvent in chemical reactions</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>55</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>52.4</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -2829,27 +2827,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Environmental contol systems (ECS)</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>55.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Solvent in chemical reactions</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>55</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>52.4</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -2860,27 +2858,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>78.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Phophating process of aluminum</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>77.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -2891,27 +2889,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Dental plaque removers</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>81.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>78.59999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81">
@@ -2922,27 +2920,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Table cloths</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>66.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Injection mould lubrication: External lubrication o ejector pins, sliders, folding units, and sliding surfaces in plastic injection moulding tools</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>42.6</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anti-stick coating and anti-stick parts in silicone moulding processes (e.g. automobile industry); coating of processing tools or moulds (function as mould release aid)</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>40.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -2953,27 +2951,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Dental plaque removers</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>81.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83">
@@ -2984,27 +2982,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Peptide manufacturing</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>76.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table cloths</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>66.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fluoropolymer films for roofing</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>59.1</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3015,27 +3013,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>78.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skin powder</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>70.59999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85">
@@ -3046,27 +3044,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>78.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trim materials</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>78.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86">
@@ -3077,27 +3075,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Dental plaque removers</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>81.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>78.59999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87">
@@ -3108,27 +3106,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dental plaque removers</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>81.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>78.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fluoropolymer processing aid for FEP</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>73.7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88">
@@ -3139,27 +3137,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Dental plaque removers</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>81.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>78.59999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89">
@@ -3170,27 +3168,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dental plaque removers</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>81.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Roofing textiles</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>78.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fluoropolymer processing aid for FEP</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>73.7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90">
@@ -3201,27 +3199,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>78.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Coatings over reactive metallic powders (e.g. aluminum)</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>70.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skin powder</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>70.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -3232,27 +3230,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fluoropolymer processing aid for FEP</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>73.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fluoropolymer processing aid for PFA</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>73.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fluoropolymer processing aid for PVF</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>73.7</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -3263,27 +3261,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>High performance upholstery</t>
+          <t>Electric circuit sealant</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>57.9</v>
+        <v>45.2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Printed circuit boards</t>
+          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>48.3</v>
+        <v>43.6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Electric circuit sealant</t>
+          <t>Lubricant for chain bearings in continuous ovens heat-treating textiles</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>45.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="93">
@@ -3294,27 +3292,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>High performance upholstery</t>
+          <t>Electric circuit sealant</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>57.9</v>
+        <v>45.2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Printed circuit boards</t>
+          <t>Warheads that require improved mechanical properties and stability at high temperatures will have the wax replaced with thermoplastics, which can include a fluorinated polymer. An example is HMX and 1,3,5‐triamino‐2,4,6‐trinitrobenzene (TATB) mixed with10 wt% fluorinated polymer.</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>48.3</v>
+        <v>43.3</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Electric circuit sealant</t>
+          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>45.2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94">
@@ -3325,27 +3323,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>Roofing textiles</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>Cleaning of metal surfaces</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Roofing textiles</t>
-        </is>
-      </c>
       <c r="E94" t="n">
-        <v>66.7</v>
+        <v>92.2</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Treatment of coatings of metal surfaces</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>64.2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95">
@@ -3356,27 +3354,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>Bedding</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>92</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Upholstery</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>Battery electrolyte solution / electrolyte additive</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Paper food straws</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Zinc batteries</t>
-        </is>
-      </c>
       <c r="G95" t="n">
-        <v>78.3</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -3391,7 +3389,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3426,19 +3424,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CT contrast agent</t>
+          <t>Refrigerant blends</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Multi-modal contrast agent</t>
+          <t>Lubricant in watch-making</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>47.1</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="98">
@@ -3449,27 +3447,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Breathing air devices</t>
+          <t>Dry-film lubricant for bike chains</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>68.8</v>
+        <v>74.7</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Clamping devices</t>
+          <t>Refrigerant blends</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>60.9</v>
+        <v>74</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>fluoropolymer binder use with TATB</t>
+          <t>Lubricant for diving gear</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>55.3</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="99">
@@ -3480,27 +3478,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>59.3</v>
+        <v>92</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Treatment of coatings of metal surfaces</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>56</v>
+        <v>89.3</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cylinder head coatings</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>53.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="100">
@@ -3515,7 +3513,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3523,15 +3521,15 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lubricant for various equipment used in wastewater treatment: chlorinators, pumps valves, etc.</t>
+          <t>Lubricant for tire moulds to reduce galling, rouging or warping at movable joints</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="101">
@@ -3585,15 +3583,15 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lubricant for various applications in helium service: oil for helium compressors and lubricants for helium regulators</t>
+          <t>Lubricant for the valves, fittings, couplings,o-rings an seals exposed to reactive and corrsive chemicals in chemicals production</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="103">
@@ -3616,7 +3614,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3624,7 +3622,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>42.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="104">
@@ -3655,7 +3653,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>49.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="105">
@@ -3678,78 +3676,78 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>43.5</v>
+        <v>42.8</v>
       </c>
       <c r="F105" t="inlineStr">
+        <is>
+          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Listed in patent for emulsions with gas-transporting properties, in particular, for intravenous administration when compensating for blood losses and for treating various diseases accompanied by hypoxic or ischemic lesions (Maevsky et al. 2003).</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lubricant for chain bearings in continuous ovens heat-treating textiles</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Lubricant for optical instruments and light housings where lubricant condensate needs to be minimized</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Listed in patent for emulsions with gas-transporting properties, in particular, for intravenous administration when compensating for blood losses and for treating various diseases accompanied by hypoxic or ischemic lesions (Maevsky et al. 2003). Listed in PFC emulsion for nitric oxide delivery to treat various conditions (Garfield et al. 1999).</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>Seals, valves, bearing coating, hose products, tank liners, gaskets and packing in food processing, medical and pharmaceutical industries, chemical and oil industries, aerospace and automotive industries, industrial equipment for sensor technology;
 Fluoropolymers are used due to high chemical and temperature resistance, high durability (reduction of friction and wear), good sliding propertie s, pressure resistance</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>42.9</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Listed in patent for emulsions with gas-transporting properties, in particular, for intravenous administration when compensating for blood losses and for treating various diseases accompanied by hypoxic or ischemic lesions (Maevsky et al. 2003).</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Anti-stick coating and anti-stick parts in silicone moulding processes (e.g. automobile industry); coating of processing tools or moulds (function as mould release aid)</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Lubricant for equpment in chlorine and bromine production, specifically vacuum pump oils, compressor oil, valve and plug cock grease, lubrication for chlorine vaporiser, valve stem lubricant, assembly and repair of chlorine cylinder valves, tank car maintenance (valves), thread lubricant</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Listed in patent for emulsions with gas-transporting properties, in particular, for intravenous administration when compensating for blood losses and for treating various diseases accompanied by hypoxic or ischemic lesions (Maevsky et al. 2003). Listed in PFC emulsion for nitric oxide delivery to treat various conditions (Garfield et al. 1999).</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>"Fluoropolymers are used as a coating on electro-nics.15,47 Numerous manufacturers refer to PFAS use on the insideand outside of electronic devices for water and oil repellence, toprotect from moisture and corrosion, to provide easy‐to‐cleansurfaces, reduces dragout in electronics, and improveappearance"</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>chains, bearings, valves, self-operated regulators, plain bearings for hinges, seat recliners, vibration dampeners, chain tensioners, shock absorbers, pumps, ropeway suspensions, dry lubricatio for the assembly of bolts, screw nuts, joints in general; various lubrication applications in systems with a high risk of contact with high oxygen concentration, devices under high vacuum</t>
-        </is>
-      </c>
       <c r="G107" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="108">
@@ -3791,27 +3789,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lubricant for the manufacture of woven wire and cable for saf use in aggressive applications</t>
+          <t>Thermal testing of semiconductor devices (in-line and end-of-line)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>48.6</v>
+        <v>49.7</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Lubricant for rack and pinion disk drive</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>Non-woven filter for oil and water separation in gas turbines</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="G109" t="n">
         <v>47.9</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Lubricant for various applications in helium service: oil for helium compressors and lubricants for helium regulators</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>47.8</v>
       </c>
     </row>
     <row r="110">
@@ -3853,27 +3851,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Acne treatment</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>78.3</v>
+        <v>92</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Solution for etching and polishing of glass</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>63.5</v>
+        <v>89.3</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Antistats in rubber and plastic compositions</t>
+          <t>Textile treatment baths</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>60.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -3884,27 +3882,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CT contrast agent</t>
+          <t>Refrigerant blends</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Multi-modal contrast agent</t>
+          <t>Lubricant in watch-making</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>47.1</v>
+        <v>72.3</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EV refrigerant circuit / EV battery system</t>
+          <t>Electronics lubricant additive</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113">
@@ -3954,19 +3952,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Marine split non-ducted units (if supplied with operating or holding charge)</t>
+          <t>Cleaning of metal surfaces</t>
         </is>
       </c>
       <c r="E114" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Lubricant in the machining of high nickel alloys</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
         <v>47.3</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Inhibitor of acid mist formation over metal electrowinning tanks</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>47.1</v>
       </c>
     </row>
     <row r="115">
@@ -3985,19 +3983,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>Refrigerant blends</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>74</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>Chemical vials</t>
         </is>
       </c>
-      <c r="E115" t="n">
+      <c r="G115" t="n">
         <v>72.7</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Beef and beef products</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -4078,19 +4076,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>Cross-linking agents for semiconductor components</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>51</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>Etching solution for piezoelectric ceramic filters</t>
         </is>
       </c>
-      <c r="E118" t="n">
+      <c r="G118" t="n">
         <v>50</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Solution for electroless plating of copper, brass and nickel</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>49.3</v>
       </c>
     </row>
     <row r="119">
@@ -4101,27 +4099,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>Protective clothing for agricultural workers (pesticide application)</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Thermal control and radiator surfaces</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>Polymer processing aids (PPAs) in the production of rubber and non-plastic packaging uses, especially in cases where thermoplastics are used</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
-        </is>
-      </c>
       <c r="G119" t="n">
-        <v>43.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="120">
@@ -4132,27 +4130,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>71.8</v>
+        <v>86.7</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Cross-linking agents for semiconductor components</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>71.40000000000001</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="121">
@@ -4163,27 +4161,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>78.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Cross-linking agents for semiconductor components</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>71.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="122">
@@ -4198,23 +4196,23 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>76.5</v>
+        <v>92.5</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Brow products</t>
+          <t>Alkaline cleaner</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>76.2</v>
+        <v>90.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hard disk drive lubricants</t>
+          <t>Industrial degreaser spray</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -4245,7 +4243,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>60.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="124">
@@ -4287,27 +4285,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Medical-grade cleaning and rinsing solvent</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>64.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Etch cleaning fluid</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>59.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jet fuel and hydrocarbon solvents</t>
+          <t>Metal cleaners</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>53.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -4318,27 +4316,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Medical-grade cleaning and rinsing solvent</t>
+          <t>Alkaline cleaner</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>64.5</v>
+        <v>90.5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Alkaline cleaner</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>60.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Etch cleaning fluid</t>
+          <t>Air filter for vaccum cleaner</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>59.3</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -4349,27 +4347,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Medical-grade cleaning and rinsing solvent</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>64.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Etch cleaning fluid</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>59.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oil coolant lines</t>
+          <t>Metal cleaners</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>58.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -4388,11 +4386,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Lubricant for power tools</t>
+          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>52.9</v>
+        <v>46.9</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4401,7 +4399,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="129">
@@ -4412,27 +4410,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Vent filter for electronic consumer devices</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>67.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cement coating</t>
+          <t>Cleaning of metal surfaces</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>66.7</v>
+        <v>86.2</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Medical-grade cleaning and rinsing solvent</t>
+          <t>Optical devices cleaners</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>64.5</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="130">
@@ -4459,11 +4457,11 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Solvent displacement drying prior to metal surface treatments</t>
+          <t>Glass surface treatment</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>51.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="131">
@@ -4474,27 +4472,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sealing systems for rotary agitators and mixers in reactive chemical processes</t>
+          <t>Protective clothing for agricultural workers (pesticide application)</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>40</v>
+        <v>56.7</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>Thermal control and radiator surfaces</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Non-woven filter for oil and water separation in gas turbines</t>
-        </is>
-      </c>
       <c r="G131" t="n">
-        <v>39.2</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="132">
@@ -4505,27 +4503,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Protective clothing for agricultural workers (pesticide application)</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>43.2</v>
+        <v>54.6</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>Thermal control and radiator surfaces</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>Fluoropolymers can be spun into fibers to make consumer andindustrial products. 26,95,251,252 --&gt; is this fluorinated plastic? Or fluoroplastics ? Or?</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>"Some PFAS areeffective blocking agents for aluminum foil, which is said to be coatedwith 0.025 g/m2 Monflor 91 applied as a 5% solution."</t>
-        </is>
-      </c>
       <c r="G132" t="n">
-        <v>40.8</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="133">
@@ -4536,27 +4534,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wetting agent / mist / fume suppressant (WM/FS) (metal plating and finishing)</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>43.6</v>
+        <v>92</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PVDF coating systems for alumnium profles, facade panels, crtain walls and architectural doors</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>43.4</v>
+        <v>89.3</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cleaning formulations removing calcium sulfate scale from reverse osmosis (RO) membranes</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>42.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="134">
@@ -4571,23 +4569,23 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>65.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t>Protective suit for firefighting</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>Aqueous film-forming foams (AFFF)</t>
         </is>
       </c>
-      <c r="E134" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Lubricant for chain bearings in continuous ovens heat-treating plastic films</t>
-        </is>
-      </c>
       <c r="G134" t="n">
-        <v>48.3</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="135">
@@ -4602,7 +4600,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4610,7 +4608,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>64.3</v>
+        <v>79.2</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4618,7 +4616,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="136">
@@ -4645,11 +4643,11 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>PTFE tape for household applications</t>
+          <t>Piping and tubing for drinking water applications</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>61.5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="137">
@@ -4660,27 +4658,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Surface treatments of porous hard surfaces</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>66.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Heat resistant packaging</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>62.5</v>
+        <v>82.8</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Frozen food packaging</t>
+          <t>Folding packaging cartons</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>60</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="138">
@@ -4691,27 +4689,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Brow products</t>
+          <t>Etch cleaning fluid</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Car care products</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>64</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Etch cleaning fluid</t>
+          <t>Metal cleaners</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>59.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -4722,27 +4720,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Printing ink additive</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>72.7</v>
+        <v>92</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>62.5</v>
+        <v>89.3</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>59.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="140">
@@ -4800,11 +4798,11 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Safety systems in transport vehicles (via semiconductors)</t>
+          <t>Filter for wasted air / incineration plants</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="142">
@@ -4831,11 +4829,11 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Safety systems in transport vehicles (via semiconductors)</t>
+          <t>Filter for wasted air / incineration plants</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="143">
@@ -4850,23 +4848,23 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Battery electrolyte solution / electrolyte additive</t>
+          <t>Iron-Flow batteries</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>67.8</v>
+        <v>79.2</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Iron-Flow batteries</t>
+          <t>Lithium-ion batteries</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>64.3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="144">
@@ -4881,23 +4879,23 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Battery electrolyte solution / electrolyte additive</t>
+          <t>Iron-Flow batteries</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>67.8</v>
+        <v>79.2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Iron-Flow batteries</t>
+          <t>Lithium-ion batteries</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>64.3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="145">
@@ -4912,23 +4910,23 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>86.2</v>
+        <v>94.7</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Peptide manufacturing</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>76.5</v>
+        <v>92</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>71.8</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="146">
@@ -4970,27 +4968,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>58.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="148">
@@ -5001,27 +4999,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cables in medical equipment</t>
+          <t>Refrigerant blends</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>54.1</v>
+        <v>74</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Lubricant in watch-making</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>47.8</v>
+        <v>72.3</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>"Machine parts have been cleanedafter nickel plating with a solution containing PFOS."</t>
+          <t>Electronics lubricant additive</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>45.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="149">
@@ -5032,27 +5030,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
+          <t>Cement coating</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Rain-repellant fluids in aviation</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
           <t>Genuine leather</t>
         </is>
       </c>
-      <c r="C149" t="n">
+      <c r="G149" t="n">
         <v>63.6</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Synthetic leather</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Fluorinated carrier solvent for analytical testing</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
-        <v>48.6</v>
       </c>
     </row>
     <row r="150">
@@ -5156,27 +5154,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Car polishes</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Brow products</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>76.2</v>
+        <v>89.3</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Floor polishes</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>72.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="154">
@@ -5191,7 +5189,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5199,7 +5197,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>64.3</v>
+        <v>79.2</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5207,7 +5205,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="155">
@@ -5218,27 +5216,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>Zinc batteries</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
           <t>Cables in medical equipment</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="E155" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Zinc batteries</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>78.3</v>
-      </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mixing equipment</t>
+          <t>Iron-Flow batteries</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>72</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="156">
@@ -5249,27 +5247,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>Aqueous film-forming foams (AFFF)</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>80</v>
+        <v>90.2</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Process additive for chemicals production</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>71.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Aqueous film-forming foams (AFFF)</t>
+          <t>Flame retardants and extinguishing agents</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>70.59999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="157">
@@ -5315,23 +5313,23 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>66.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>fluoropolymer binder use with RDX</t>
+          <t>PTFE micropowder</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>56.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>fluoropolymer binder use with TATB</t>
+          <t>PTFE strip (aerospace)</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>55.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="159">
@@ -5350,19 +5348,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>fluoropolymer binder use with RDX</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>59.1</v>
+        <v>56.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>fluoropolymer binder use with RDX</t>
+          <t>fluoropolymer binder use with TATB</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>56.5</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="160">
@@ -5373,27 +5371,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Cement coating</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Rain-repellant fluids in aviation</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>58.8</v>
+        <v>65.3</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Non-woven filter for oil and water separation in gas turbines</t>
+          <t>Sol-gel coating</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>54.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="161">
@@ -5435,27 +5433,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mobile air conditioning (MAC) unit for cars</t>
+          <t>Refrigerant blends</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>49.6</v>
+        <v>74</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Self-contained aircraft refrigeration unit</t>
+          <t>Lubricant in watch-making</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>48.3</v>
+        <v>72.3</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Self-contained commercial refrigerator</t>
+          <t>Electronics lubricant additive</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>44.8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="163">
@@ -5466,27 +5464,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Refrigerant blends</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>44.4</v>
+        <v>74</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>EV refrigerant circuit / EV battery system</t>
+          <t>Lubricant in watch-making</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>44</v>
+        <v>72.3</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>hydrophobic and/or oleophobic filtration membranes, coated in PFAS-related chemistries to alter their surface tension properties, used in pharmaceutical processing to prevent the passage of microorganisms such as bacteria and endotoxins</t>
+          <t>Electronics lubricant additive</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>43.8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="164">
@@ -5497,27 +5495,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>58.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="165">
@@ -5528,27 +5526,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Acne treatment</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>78.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Heat resistant packaging</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>62.5</v>
+        <v>82.8</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Frozen food packaging</t>
+          <t>Folding packaging cartons</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>60</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="166">
@@ -5598,19 +5596,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>Lubricant of moveable parts e.g., bearings, jewels, and pivots in many instruments/equipment</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
           <t>Grease for swivel joints in the oxygen heating and delivery systems in steel production</t>
         </is>
       </c>
-      <c r="E167" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Lubricant for equipment used in the fluorination process for blow-moulding PE bottles and gasoline tanks</t>
-        </is>
-      </c>
       <c r="G167" t="n">
-        <v>43.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="168">
@@ -5621,27 +5619,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>Etch cleaning fluid</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
           <t>Dishes and glass cleaners</t>
         </is>
       </c>
-      <c r="C168" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Polymer processing aids (PPAs) in the extrusion of PP, PE, and polyolefin films</t>
-        </is>
-      </c>
       <c r="E168" t="n">
-        <v>48.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fluorinated industrial metal cleaning and degreasing solvent</t>
+          <t>Glass cleaners</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>47.8</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -5652,27 +5650,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Furnace components</t>
+          <t>Protective suit for firefighting</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cleaner for adhesives</t>
+          <t>Streaming fire-extinguishing agent</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>60</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Flame retardants and extinguishing agents</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>57.1</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -5683,27 +5681,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>62.5</v>
+        <v>92</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Baking paper</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>58.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="171">
@@ -5730,11 +5728,11 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>O&amp;G pipe gaskets</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>85.7</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -5753,19 +5751,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Solvents in chemical production</t>
+          <t>fluoropolymer binder use with RDX</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>59.1</v>
+        <v>56.5</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>fluoropolymer binder use with RDX</t>
+          <t>fluoropolymer binder use with TATB</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>56.5</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="173">
@@ -5900,27 +5898,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paper food straws</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>78.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kraft paper</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>62.5</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="178">
@@ -5931,27 +5929,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Blood bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>57.1</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ostomy bags</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>53.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Leather bags</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>50</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="179">
@@ -5962,27 +5960,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Pet food bags</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Blood bags</t>
+          <t>Frozen food packaging</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>57.1</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dye transfer material</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>55.2</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -6001,19 +5999,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Anti-reflection coatings in semiconductor production</t>
+          <t>Anti-corrosion coating for industrial tanks and pipelines</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>45.6</v>
+        <v>45.4</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Anti-corrosion coating for industrial tanks and pipelines</t>
+          <t>Wind turbine blade protection coating</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>45.4</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="181">
@@ -6063,19 +6061,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PBSF surfactant</t>
+          <t>PC/ABS plastic semiconductor components</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pipes and pipe components</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>71.8</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="183">
@@ -6125,19 +6123,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Grease for swivel joints in the oxygen heating and delivery systems in steel production</t>
+          <t>Perfumes and fragrances</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Textile treatment sprays and creams (leather and others)</t>
+          <t>Finishing and top coat in metal product manufacturing</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="185">
@@ -6148,27 +6146,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fibre finishes</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>72.7</v>
+        <v>92</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Glassfiber coatings</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>59.3</v>
+        <v>89.3</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cylinder head coatings</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>53.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="186">
@@ -6210,11 +6208,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fluorinated carrier solvent for lubricant deposition</t>
+          <t>Extruded polystyrene foam (XPS) boards</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>52.2</v>
+        <v>48.3</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -6226,11 +6224,11 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Etching solution for the SiO2 coating of the semiconductor device</t>
+          <t>Hard chrome plating solution (metal plating)</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="188">
@@ -6272,27 +6270,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Printed circuit boards</t>
+          <t>Electric circuit sealant</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>48.3</v>
+        <v>45.2</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Cleaning formulations removing calcium sulfate scale from reverse osmosis (RO) membranes</t>
+          <t>Printed circuit board (PCB) matrix</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>46.7</v>
+        <v>44.4</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vacuum pump oil for equipment used to plasma-desmear multilayer printed circuit boards</t>
+          <t>Cured epoxy resin remover</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="190">
@@ -6303,27 +6301,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Non-woven filter for oil and water separation in gas turbines</t>
+          <t>Hair spray</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>49.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Lubricant encased within peristaltic pumps which are used in applications of the potable water industry for chemical dosing</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>49.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Aluminum coated with PFAS are also cited for use as propellants in solid rocket propellants and ramjet fuel for civilian and militarypurposes. (p 360)</t>
+          <t>Deodorant spray</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>48.6</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -6334,27 +6332,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ball valve</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>66.7</v>
+        <v>86.7</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Gate valve</t>
+          <t>Printed circuit boards</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>66.7</v>
+        <v>86.2</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Plug valve</t>
+          <t>Multilayer circuit board</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>66.7</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="192">
@@ -6365,27 +6363,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cyrogenic storage tanks</t>
+          <t>Solder mask</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>72.2</v>
+        <v>86.7</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>O&amp;G tanks</t>
+          <t>Printed circuit boards</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>71.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ball valve</t>
+          <t>Multilayer circuit board</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>66.7</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="193">
@@ -6396,27 +6394,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ball valve</t>
+          <t>Bedding</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>66.7</v>
+        <v>92</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Gate valve</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>66.7</v>
+        <v>89.3</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Plug valve</t>
+          <t>Drive belts</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>66.7</v>
+        <v>88.5</v>
       </c>
     </row>
   </sheetData>
@@ -6430,7 +6428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -6472,17 +6470,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Before scoring, both sides are expanded with a domain synonym dictionary (scripts/matching_utils.py) so e.g. a clothing-item name</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>matches a general 'clothing/apparel' taxonomy entry, and PFAS-chemistry abbreviations match their spelled-out form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>A high score means the two text strings share most of their words; it is NOT a chemical or regulatory equivalence claim.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Scores below ~50 are generally weak matches and should be treated as 'no good match found' -- spot-check before relying on them.</t>
         </is>
